--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,17 +429,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id_equipo_real</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>nombre_equipo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>alias_equipo</t>
         </is>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -584,119 +584,119 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Athletic de Bilbao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>ATH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Athletic de Bilbao</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -533,51 +533,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CEL</t>
+          <t>GET</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RSO</t>
+          <t>CEL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>RSO</t>
         </is>
       </c>
     </row>
@@ -618,17 +618,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
@@ -652,102 +652,102 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -686,68 +686,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -618,68 +618,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -584,153 +584,153 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Athletic de Bilbao</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Athletic de Bilbao</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>ATH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -652,34 +652,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -686,51 +686,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -533,85 +533,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>CEL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CEL</t>
+          <t>GET</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic de Bilbao</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RSO</t>
+          <t>ATH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>RSO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Athletic de Bilbao</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
@@ -635,34 +635,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -635,34 +635,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -720,34 +720,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -737,34 +737,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -567,34 +567,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Athletic de Bilbao</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>RSO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic de Bilbao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RSO</t>
+          <t>ATH</t>
         </is>
       </c>
     </row>
@@ -635,136 +635,136 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -635,85 +635,85 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -601,34 +601,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
@@ -669,17 +669,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
@@ -703,17 +703,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -703,68 +703,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -601,170 +601,170 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -601,68 +601,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
@@ -686,85 +686,85 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -567,153 +567,153 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RSO</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Athletic de Bilbao</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RSO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Athletic de Bilbao</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>ATH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ALA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
@@ -737,34 +737,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -686,85 +686,85 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>51b889b1e401a15f2c0000f0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Elche</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>ELC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000cf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>LEV</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000d1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>OSA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>

--- a/datos/maestros/md_equipos.xlsx
+++ b/datos/maestros/md_equipos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,340 +448,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c7</t>
+          <t>504e581e4d8bec9a670000d2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FCB</t>
+          <t>MLL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c6</t>
+          <t>520347e4b8d07d930b00000f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RMA</t>
+          <t>GIR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>51b890f5b986415a2c000012</t>
+          <t>51ffb00e78b20d7f0700003f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>R. Oviedo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VIL</t>
+          <t>ROV</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c8</t>
+          <t>520e4ee4a776cc826b00004b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atlético de Madrid</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ATM</t>
+          <t>RAC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cc</t>
+          <t>504e581e4d8bec9a670000c7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BET</t>
+          <t>FCB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d9</t>
+          <t>504e581e4d8bec9a670000d8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo de la Coruña</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CEL</t>
+          <t>DEP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cd</t>
+          <t>504e581e4d8bec9a670000c6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>RMA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ca</t>
+          <t>51b890f5b986415a2c000012</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>VIL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cb</t>
+          <t>504e581e4d8bec9a670000d6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>MAL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000ce</t>
+          <t>504e581e4d8bec9a670000c8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético de Madrid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RSO</t>
+          <t>ATM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d0</t>
+          <t>504e581e4d8bec9a670000cc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>BET</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000c9</t>
+          <t>504e581e4d8bec9a670000d9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Athletic de Bilbao</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CEL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d5</t>
+          <t>504e581e4d8bec9a670000cd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEV</t>
+          <t>GET</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52038563b8d07d930b00008a</t>
+          <t>504e581e4d8bec9a670000ca</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>RVA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51b889b1e401a15f2c0000f0</t>
+          <t>504e581e4d8bec9a670000cb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ELC</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000cf</t>
+          <t>504e581e4d8bec9a670000ce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LEV</t>
+          <t>RSO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d1</t>
+          <t>504e581e4d8bec9a670000d0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OSA</t>
+          <t>ESP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>504e581e4d8bec9a670000d2</t>
+          <t>504e581e4d8bec9a670000c9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Athletic de Bilbao</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MLL</t>
+          <t>ATH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>520347e4b8d07d930b00000f</t>
+          <t>504e581e4d8bec9a670000d5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GIR</t>
+          <t>SEV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51ffb00e78b20d7f0700003f</t>
+          <t>52038563b8d07d930b00008a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R. Oviedo</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ROV</t>
+          <t>ALA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>51b889b1e401a15f2c0000f0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ELC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000cf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LEV</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>504e581e4d8bec9a670000d1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OSA</t>
         </is>
       </c>
     </row>
